--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_283_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_283_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1471</v>
+        <v>7.4343</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5529</v>
+        <v>4.5712</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5943</v>
+        <v>2.8631</v>
       </c>
       <c r="G2" t="n">
         <v>6.6381</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.8519</v>
+        <v>-1.5648</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5525</v>
+        <v>-0.5342</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2994</v>
+        <v>-1.0306</v>
       </c>
       <c r="V2" t="n">
         <v>3.7527</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1154</v>
+        <v>4.3252</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0997</v>
+        <v>4.4103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0158</v>
+        <v>-0.0851</v>
       </c>
       <c r="G3" t="n">
         <v>1.6233</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0593</v>
+        <v>0.1505</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1458</v>
+        <v>0.4564</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2051</v>
+        <v>-0.306</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3999</v>
+        <v>3.0968</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9842</v>
+        <v>1.7482</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4158</v>
+        <v>1.3485</v>
       </c>
       <c r="G4" t="n">
         <v>2.2771</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.427</v>
+        <v>0.1239</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3541</v>
+        <v>0.1182</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1027</v>
+        <v>0.1806</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6724</v>
+        <v>-1.2632</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7751</v>
+        <v>1.4437</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7309</v>
+        <v>1.4625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7169</v>
+        <v>1.1814</v>
       </c>
       <c r="I5" t="n">
-        <v>1.014</v>
+        <v>0.2811</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7243</v>
+        <v>0.3761</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9649</v>
+        <v>0.3025</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7595</v>
+        <v>0.0736</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0065</v>
+        <v>1.0864</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.248</v>
+        <v>0.8789</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2545</v>
+        <v>0.2075</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0876</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1759</v>
+        <v>-0.4443</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8169</v>
+        <v>-0.4795</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3589</v>
+        <v>0.0351</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2836</v>
+        <v>-0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4254</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2172</v>
+        <v>0.1658</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2257</v>
+        <v>-0.5795</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4428</v>
+        <v>0.7453</v>
       </c>
       <c r="G6" t="n">
         <v>2.3269</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5531</v>
+        <v>-0.6045</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2715</v>
+        <v>-0.0824</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8246</v>
+        <v>-0.5221</v>
       </c>
       <c r="V6" t="n">
         <v>-1.3247</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0626</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3811</v>
+        <v>0.7786</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4437</v>
+        <v>-0.6805</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4625</v>
+        <v>3.8425</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1814</v>
+        <v>0.4464</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2811</v>
+        <v>3.3961</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3761</v>
+        <v>3.7929</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3025</v>
+        <v>0.3367</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0736</v>
+        <v>3.4561</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0864</v>
+        <v>0.0497</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8789</v>
+        <v>0.1097</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2075</v>
+        <v>-0.06</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5623</v>
+        <v>-1.5589</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5975</v>
+        <v>-0.8134</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0351</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>-2.6495</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.0412</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7679</v>
+        <v>-0.3141</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1142</v>
+        <v>-2.249</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8821</v>
+        <v>1.935</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8425</v>
+        <v>1.7309</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4464</v>
+        <v>0.7169</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3961</v>
+        <v>1.014</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7929</v>
+        <v>1.7243</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3367</v>
+        <v>0.9649</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4561</v>
+        <v>0.7595</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0497</v>
+        <v>0.0065</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1097</v>
+        <v>-0.248</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06</v>
+        <v>0.2545</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.4249</v>
+        <v>-0.241</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4778</v>
+        <v>0.2403</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.4812</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.6495</v>
+        <v>0.2836</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0412</v>
+        <v>0.4254</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7801</v>
+        <v>-0.603</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0569</v>
+        <v>-0.4337</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2768</v>
+        <v>-0.1693</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3909</v>
+        <v>-0.6158</v>
       </c>
       <c r="H9" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.6424</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.5047</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.1344</v>
       </c>
-      <c r="I9" t="n">
-        <v>-0.5253</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.7661</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0203</v>
-      </c>
       <c r="L9" t="n">
-        <v>-0.7863</v>
+        <v>-0.6391</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3752</v>
+        <v>-0.1111</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1141</v>
+        <v>-0.1078</v>
       </c>
       <c r="O9" t="n">
-        <v>0.261</v>
+        <v>-0.0033</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3892</v>
+        <v>-0.9151</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2908</v>
+        <v>0.0709</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0984</v>
+        <v>-0.986</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9905</v>
+        <v>-0.6621</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7876</v>
+        <v>-0.9389</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2029</v>
+        <v>0.2768</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6158</v>
+        <v>-0.3909</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0266</v>
+        <v>0.1344</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6424</v>
+        <v>-0.5253</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5047</v>
+        <v>-0.7661</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1344</v>
+        <v>0.0203</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6391</v>
+        <v>-0.7863</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1111</v>
+        <v>0.3752</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1078</v>
+        <v>0.1141</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0033</v>
+        <v>0.261</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3025</v>
+        <v>-0.2713</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2829</v>
+        <v>-0.1729</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0196</v>
+        <v>-0.0984</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5765</v>
+        <v>-2.1143</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6977</v>
+        <v>-3.2691</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1212</v>
+        <v>1.1548</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5963</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2095</v>
+        <v>0.2526</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0114</v>
+        <v>0.4171</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1981</v>
+        <v>-0.1645</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4665</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.074</v>
+        <v>-4.3778</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8211</v>
+        <v>-3.2929</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.253</v>
+        <v>-1.0849</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2895</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8746</v>
+        <v>-1.1784</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1019</v>
+        <v>-0.5737</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.6047</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1418</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.8559</v>
+        <v>7.229499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8914999999999993</v>
+        <v>-0.5180000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>7.7475</v>
+        <v>7.7474</v>
       </c>
       <c r="G13" t="n">
         <v>14.0088</v>
       </c>
       <c r="H13" t="n">
-        <v>6.129</v>
+        <v>6.129000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>7.879799999999999</v>
@@ -1456,7 +1456,7 @@
         <v>3.3165</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.04899999999999999</v>
+        <v>-0.04900000000000004</v>
       </c>
       <c r="P13" t="n">
         <v>1.1598</v>
@@ -1468,13 +1468,13 @@
         <v>16.2367</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.624400000000001</v>
+        <v>-6.2513</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7265</v>
+        <v>-1.3532</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.8981</v>
+        <v>-4.8982</v>
       </c>
       <c r="V13" t="n">
         <v>-1.688</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7589</v>
+        <v>5.5051</v>
       </c>
       <c r="E14" t="n">
-        <v>9.7782</v>
+        <v>3.2277</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0192</v>
+        <v>2.2774</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3263</v>
+        <v>2.027</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4032</v>
+        <v>0.4442</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0769</v>
+        <v>1.5827</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2992</v>
+        <v>2.2023</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5325</v>
+        <v>0.8773</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7666</v>
+        <v>1.325</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9729</v>
+        <v>-0.1754</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1294</v>
+        <v>-0.4331</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8435</v>
+        <v>0.2578</v>
       </c>
       <c r="P14" t="n">
         <v>1.1598</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9508</v>
+        <v>0.9937</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1928</v>
+        <v>0.1852</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.242</v>
+        <v>0.8085</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.3247</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7501</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.428</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.611</v>
+        <v>5.4722</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3457</v>
+        <v>8.008900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2653</v>
+        <v>-2.5367</v>
       </c>
       <c r="G15" t="n">
-        <v>2.027</v>
+        <v>3.3263</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4442</v>
+        <v>3.4032</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5827</v>
+        <v>-0.0769</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2023</v>
+        <v>5.2992</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8773</v>
+        <v>3.5325</v>
       </c>
       <c r="L15" t="n">
-        <v>1.325</v>
+        <v>1.7666</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1754</v>
+        <v>-1.9729</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4331</v>
+        <v>-0.1294</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2578</v>
+        <v>-1.8435</v>
       </c>
       <c r="P15" t="n">
         <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0996</v>
+        <v>1.6641</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3031</v>
+        <v>1.4235</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7965</v>
+        <v>0.2405</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3247</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>1.7501</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2525</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.728</v>
+        <v>0.6722</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7478</v>
+        <v>0.5119</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0198</v>
+        <v>0.1603</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5871</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1527</v>
+        <v>1.0969</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5351</v>
+        <v>0.2992</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6177</v>
+        <v>0.7978</v>
       </c>
       <c r="V16" t="n">
         <v>0.3943</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.4417</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3678</v>
+        <v>-2.4857</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6958</v>
+        <v>2.044</v>
       </c>
       <c r="G17" t="n">
         <v>0.316</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1718</v>
+        <v>0.402</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0171</v>
+        <v>0.331</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0437</v>
+        <v>-0.6571</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1359</v>
+        <v>-1.0164</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.3593</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7741</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8155</v>
+        <v>0.2029</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5897</v>
+        <v>-1.0673</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6997</v>
+        <v>-0.6823</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0007</v>
+        <v>0.0672</v>
       </c>
       <c r="L18" t="n">
-        <v>3.7003</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9255</v>
+        <v>-0.1821</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1852</v>
+        <v>0.1357</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1107</v>
+        <v>-0.3178</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.0307</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.4224</v>
+        <v>-0.4639</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2103</v>
+        <v>0.4393</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2284</v>
+        <v>0.1298</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9819</v>
+        <v>0.3095</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0026</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1574</v>
+        <v>-0.8908</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3703</v>
+        <v>-1.018</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2128</v>
+        <v>0.1272</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8643999999999999</v>
+        <v>1.7741</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2029</v>
+        <v>-0.8155</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0673</v>
+        <v>2.5897</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6823</v>
+        <v>2.6997</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0672</v>
+        <v>-1.0007</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7495000000000001</v>
+        <v>3.7003</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1821</v>
+        <v>-0.9255</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1357</v>
+        <v>0.1852</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3178</v>
+        <v>-1.1107</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>-6.0307</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4639</v>
+        <v>-7.4224</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0611</v>
+        <v>1.3631</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>0.3464</v>
       </c>
       <c r="U19" t="n">
-        <v>0.163</v>
+        <v>1.0168</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.0026</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0139</v>
+        <v>-1.3892</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3386</v>
+        <v>-2.4303</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3248</v>
+        <v>1.0411</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7185</v>
+        <v>-2.3996</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4766</v>
+        <v>-0.8571</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2418</v>
+        <v>-1.5425</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9028</v>
+        <v>-2.0138</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3472</v>
+        <v>-1.4214</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5556</v>
+        <v>-0.5924</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8156</v>
+        <v>-0.3858</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1294</v>
+        <v>0.5644</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6862</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0757</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8837</v>
+        <v>0.0474</v>
       </c>
       <c r="U20" t="n">
-        <v>0.192</v>
+        <v>0.0351</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4063</v>
+        <v>-1.5584</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2756</v>
+        <v>-0.6858</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1307</v>
+        <v>-0.8726</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3162</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.554</v>
+        <v>0.2939</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>0.4404</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4046</v>
+        <v>-0.1465</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9162</v>
+        <v>-2.8009</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3739</v>
+        <v>-3.5182</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4577</v>
+        <v>0.7173</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3996</v>
+        <v>-3.7185</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8571</v>
+        <v>-1.4766</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5425</v>
+        <v>-2.2418</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0138</v>
+        <v>-1.9028</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4214</v>
+        <v>-1.3472</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5924</v>
+        <v>-0.5556</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3858</v>
+        <v>-1.8156</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5644</v>
+        <v>-0.1294</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.6862</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4444</v>
+        <v>1.2887</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>0.7042</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5482</v>
+        <v>0.5845</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5525</v>
+        <v>-2.8061</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4663</v>
+        <v>-3.1125</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0862</v>
+        <v>0.3064</v>
       </c>
       <c r="G23" t="n">
         <v>-5.599</v>
@@ -2248,13 +2248,13 @@
         <v>2.5515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2631</v>
+        <v>1.0095</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3857</v>
+        <v>0.7395</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1226</v>
+        <v>0.27</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1919</v>
+        <v>-4.8158</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2906</v>
+        <v>-5.2291</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0987</v>
+        <v>0.4133</v>
       </c>
       <c r="G24" t="n">
         <v>-6.9674</v>
@@ -2326,13 +2326,13 @@
         <v>2.3195</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2399</v>
+        <v>1.1362</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.55</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3102</v>
+        <v>0.6247</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8559</v>
+        <v>-3.710500000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.747300000000001</v>
+        <v>-7.747499999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8914999999999995</v>
+        <v>4.036999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-14.0088</v>
@@ -2377,7 +2377,7 @@
         <v>-7.8797</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.2675</v>
+        <v>-3.267499999999999</v>
       </c>
       <c r="K25" t="n">
         <v>-3.316699999999999</v>
@@ -2392,10 +2392,10 @@
         <v>-2.8125</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.928599999999999</v>
+        <v>-7.9286</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1598</v>
+        <v>-1.159800000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.2367</v>
@@ -2404,13 +2404,13 @@
         <v>15.077</v>
       </c>
       <c r="S25" t="n">
-        <v>6.624599999999999</v>
+        <v>9.770000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>4.898099999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7268</v>
+        <v>4.871899999999999</v>
       </c>
       <c r="V25" t="n">
         <v>1.6879</v>
